--- a/Result/profitability/2426.xlsx
+++ b/Result/profitability/2426.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.01</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.04750000000000003</v>
+        <v>-0.02375000000000003</v>
       </c>
       <c r="N2" t="n">
-        <v>12.59875</v>
+        <v>13.3825</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.3</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.01375000000000003</v>
+        <v>0.03999999999999997</v>
       </c>
       <c r="N3" t="n">
-        <v>11.8125</v>
+        <v>14.2025</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.13</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02874999999999997</v>
+        <v>0.05749999999999997</v>
       </c>
       <c r="N4" t="n">
-        <v>12.5925</v>
+        <v>13.64875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.47</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.02875000000000003</v>
+        <v>0.007499999999999979</v>
       </c>
       <c r="N5" t="n">
-        <v>10.74625</v>
+        <v>11.85625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.28</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.05500000000000003</v>
+        <v>-0.01375000000000003</v>
       </c>
       <c r="N6" t="n">
-        <v>7.2925</v>
+        <v>8.785</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.11</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.05500000000000003</v>
+        <v>-0.01750000000000003</v>
       </c>
       <c r="N7" t="n">
-        <v>7.24375</v>
+        <v>8.7075</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.11</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.03125000000000003</v>
+        <v>-0.01125000000000003</v>
       </c>
       <c r="N8" t="n">
-        <v>7.355</v>
+        <v>7.712499999999999</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>0.06</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04624999999999997</v>
+        <v>0.04624999999999998</v>
       </c>
       <c r="N10" t="n">
         <v>5.7475</v>
@@ -1772,7 +1772,7 @@
         <v>0.15</v>
       </c>
       <c r="M11" t="n">
-        <v>0.02749999999999997</v>
+        <v>0.02749999999999998</v>
       </c>
       <c r="N11" t="n">
         <v>6.22875</v>
@@ -1899,10 +1899,10 @@
         <v>0.38</v>
       </c>
       <c r="M12" t="n">
-        <v>0.05874999999999997</v>
+        <v>0.05874999999999998</v>
       </c>
       <c r="N12" t="n">
-        <v>6.924999999999999</v>
+        <v>6.925</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -2026,10 +2026,10 @@
         <v>-0.14</v>
       </c>
       <c r="M13" t="n">
-        <v>0.09999999999999996</v>
+        <v>0.09999999999999998</v>
       </c>
       <c r="N13" t="n">
-        <v>7.915</v>
+        <v>7.914999999999999</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2426</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>692</v>
+      </c>
+      <c r="D75" t="n">
+        <v>536</v>
+      </c>
+      <c r="E75" t="n">
+        <v>156</v>
+      </c>
+      <c r="F75" t="n">
+        <v>22.49</v>
+      </c>
+      <c r="G75" t="n">
+        <v>56</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>8.04%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>11</v>
+      </c>
+      <c r="J75" t="n">
+        <v>67</v>
+      </c>
+      <c r="K75" t="n">
+        <v>67</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.02125000000000003</v>
+      </c>
+      <c r="N75" t="n">
+        <v>13.83625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.859999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1456953642384107</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-4.142857142857142</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>8.879999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.6524614254224834</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
